--- a/Assignment1_HT.xlsx
+++ b/Assignment1_HT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentGeorgeTolkach\Desktop\CG_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8853DD4D-91B6-48EE-A1B8-9FF2A7725961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6503E64C-5135-495F-8D22-6E2E2361E1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -559,44 +559,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -622,23 +622,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>593910</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>89645</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1748118</xdr:colOff>
+      <xdr:colOff>1810537</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>5129563</xdr:rowOff>
+      <xdr:rowOff>5154707</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB41D6B9-7C54-DF9E-E2BF-CA2760AA4C93}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C970CF89-38B9-269D-4D73-EC0C4B2ECF8F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -646,17 +646,16 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
+      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect l="-3951" r="39737"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1804145" y="403410"/>
-          <a:ext cx="1759326" cy="5039918"/>
+          <a:off x="1815353" y="313766"/>
+          <a:ext cx="1810537" cy="5154706"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -668,22 +667,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1692088</xdr:colOff>
+      <xdr:colOff>1692089</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>112057</xdr:rowOff>
+      <xdr:rowOff>11208</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1255058</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>42761</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>1613647</xdr:rowOff>
+      <xdr:rowOff>4011706</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62A65F92-1343-606E-0687-2E28E751221B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8422326-FB7B-3B65-C523-5098A4492CB5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -691,17 +690,16 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
+      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:srcRect t="78986" r="19608"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3507441" y="425822"/>
-          <a:ext cx="2073088" cy="1501590"/>
+          <a:off x="3507442" y="324973"/>
+          <a:ext cx="2127054" cy="4000498"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -713,22 +711,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>324970</xdr:colOff>
+      <xdr:colOff>739588</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
+      <xdr:rowOff>156883</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>863277</xdr:colOff>
+      <xdr:colOff>782526</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1558381</xdr:rowOff>
+      <xdr:rowOff>1614411</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{612A8402-1A1D-7BBC-887A-8945B35FC80A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFAB4443-2214-0E6E-7AEC-C1F5FFC04853}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -744,8 +742,363 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2140323" y="5916706"/>
-          <a:ext cx="3048425" cy="1457528"/>
+          <a:off x="2554941" y="5972736"/>
+          <a:ext cx="2553056" cy="1457528"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>201708</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1860176</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>5188325</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62C6102E-A7A4-E9E4-0350-9E4643359D55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:srcRect r="9564"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1815354" y="7933767"/>
+          <a:ext cx="1860175" cy="5221940"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1860177</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>224120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1232647</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>4244730</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6D012E3-A423-E292-D6DF-47BDA28331F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:srcRect r="14647"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3675530" y="7956179"/>
+          <a:ext cx="1882588" cy="4255933"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>627530</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>11209</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>896470</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1165412</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84E6FF8B-CF2C-4C4E-7C78-9D6EAC438BB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2442883" y="13491885"/>
+          <a:ext cx="2779058" cy="1154203"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>78442</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1793803</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>4971280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8BC7430-4BAC-25E0-ADEF-7175118509BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1893795" y="15060706"/>
+          <a:ext cx="1715361" cy="4881633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1792943</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>38763</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>3944471</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7868C7E-6AA6-DDCB-922C-64B8A9885F0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3608296" y="15071912"/>
+          <a:ext cx="2022202" cy="3843618"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>526679</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>694764</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>16753</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C6B44D0-51E2-7037-C21A-32B29836F060}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2342032" y="20473147"/>
+          <a:ext cx="2678203" cy="1395077"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>33620</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>78441</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1843231</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{672C0E0C-CDFA-94BA-1EE0-8DA9D3C21A4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1848973" y="22243676"/>
+          <a:ext cx="1809611" cy="5143500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1882593</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>78441</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1242649</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>4258236</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31CAA55F-30E4-A37E-E396-8137F17D9156}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:srcRect r="11346"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3697946" y="22243676"/>
+          <a:ext cx="1870174" cy="4179795"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1057,24 +1410,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1086,7 +1439,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="26">
-        <v>366252</v>
+        <v>262291</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1098,7 +1451,7 @@
       </c>
       <c r="C6" s="27">
         <f>MOD(C4,100)-50</f>
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1110,22 +1463,22 @@
       </c>
       <c r="C7" s="28">
         <f>C21/$G$21</f>
-        <v>0.99076429675591937</v>
+        <v>0.98019605881960692</v>
       </c>
       <c r="D7" s="27">
         <f t="shared" ref="D7:E7" si="0">D21/$G$21</f>
-        <v>-9.5880415815088965E-2</v>
+        <v>-0.140028008402801</v>
       </c>
       <c r="E7" s="29">
         <f t="shared" si="0"/>
-        <v>-9.5880415815088965E-2</v>
+        <v>-0.140028008402801</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>37</v>
       </c>
       <c r="G7" s="33">
         <f>C21</f>
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H7" s="25">
         <f t="shared" ref="H7:I7" si="1">D21</f>
@@ -1148,11 +1501,11 @@
       </c>
       <c r="C8" s="28">
         <f>C22</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="27">
         <f t="shared" ref="D8:E8" si="2">D22</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="29">
         <f t="shared" si="2"/>
@@ -1168,11 +1521,11 @@
       </c>
       <c r="C9" s="28">
         <f>C23</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D9" s="27">
         <f t="shared" ref="D9:E9" si="3">D23</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E9" s="29">
         <f t="shared" si="3"/>
@@ -1191,7 +1544,7 @@
       </c>
       <c r="C11" s="28">
         <f>C25</f>
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D11" s="27">
         <f t="shared" ref="D11:E11" si="4">D25</f>
@@ -1213,7 +1566,7 @@
       </c>
       <c r="D12" s="36">
         <f t="shared" ref="D12:E12" si="5">D26</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" s="29">
         <f t="shared" si="5"/>
@@ -1230,15 +1583,15 @@
       </c>
       <c r="C13" s="28">
         <f>C27/$G$27</f>
-        <v>-6.4084133611200148E-2</v>
+        <v>-9.3864650892786422E-2</v>
       </c>
       <c r="D13" s="27">
         <f t="shared" ref="D13:E13" si="6">D27/$G$27</f>
-        <v>-9.6126200416800214E-2</v>
+        <v>-0.14079697633917962</v>
       </c>
       <c r="E13" s="29">
         <f t="shared" si="6"/>
-        <v>0.99330407097360229</v>
+        <v>0.98557883437425742</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>32</v>
@@ -1253,7 +1606,7 @@
       </c>
       <c r="I13" s="34">
         <f t="shared" si="7"/>
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J13" s="35" t="s">
         <v>39</v>
@@ -1297,7 +1650,7 @@
     <row r="21" spans="1:7" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="31">
         <f>INT((C4/10000))-5</f>
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D21" s="31">
         <f>MOD(INT((C4/100)),10)-5</f>
@@ -1309,17 +1662,17 @@
       </c>
       <c r="G21" s="25">
         <f>SQRT(C21*C21+D21*D21+E21*E21)</f>
-        <v>31.28897569432403</v>
+        <v>21.42428528562855</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="32">
         <f>MOD(INT((C4/10000)),6) + 1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="32">
         <f>MOD(MOD(INT((C4/1000)),10),6) +1</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="32">
         <f>MOD(MOD(INT((C4/100)),10),6) +1</f>
@@ -1327,17 +1680,17 @@
       </c>
       <c r="G22" s="25">
         <f t="shared" ref="G22:G27" si="8">SQRT(C22*C22+D22*D22+E22*E22)</f>
-        <v>3.3166247903553998</v>
+        <v>5.196152422706632</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="27">
         <f>MOD(C4,10)-5</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="D23" s="27">
         <f>MOD(INT((C4/10)),10)-5</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E23" s="27">
         <f>MOD(INT((C4/100)),10)-4</f>
@@ -1345,7 +1698,7 @@
       </c>
       <c r="G23" s="25">
         <f t="shared" si="8"/>
-        <v>3.6055512754639891</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1357,7 +1710,7 @@
     <row r="25" spans="1:7" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="27">
         <f>2+C21</f>
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D25" s="27">
         <f>3+D21</f>
@@ -1369,7 +1722,7 @@
       </c>
       <c r="G25" s="25">
         <f t="shared" si="8"/>
-        <v>57.428216061444921</v>
+        <v>52.32590180780452</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1379,7 +1732,7 @@
       </c>
       <c r="D26" s="31">
         <f>C22</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" s="31">
         <f>E22</f>
@@ -1387,7 +1740,7 @@
       </c>
       <c r="G26" s="25">
         <f t="shared" si="8"/>
-        <v>4.358898943540674</v>
+        <v>5.196152422706632</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1402,11 +1755,11 @@
       </c>
       <c r="E27" s="31">
         <f>C21</f>
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G27" s="25">
         <f t="shared" si="8"/>
-        <v>31.208973068654469</v>
+        <v>21.307275752662516</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1456,10 +1809,10 @@
     </row>
     <row r="2" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="4"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="43"/>
+      <c r="E2" s="47"/>
       <c r="F2" s="7"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1470,8 +1823,8 @@
     </row>
     <row r="3" spans="3:13" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="4"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="5"/>
       <c r="G3" s="10"/>
       <c r="H3" s="6"/>
@@ -1491,10 +1844,10 @@
     </row>
     <row r="5" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="4"/>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="43"/>
+      <c r="E5" s="47"/>
       <c r="F5" s="7"/>
       <c r="H5" s="14"/>
       <c r="I5" s="11"/>
@@ -1503,8 +1856,8 @@
     </row>
     <row r="6" spans="3:13" ht="138.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="4"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="41"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="40"/>
       <c r="F6" s="15"/>
       <c r="G6" s="11"/>
       <c r="H6" s="14"/>
@@ -1524,10 +1877,10 @@
     </row>
     <row r="8" spans="3:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="4"/>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="43"/>
+      <c r="E8" s="47"/>
       <c r="F8" s="16"/>
       <c r="G8" s="11"/>
       <c r="H8" s="14"/>
@@ -1537,8 +1890,8 @@
     </row>
     <row r="9" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="4"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="41"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="40"/>
       <c r="F9" s="16"/>
       <c r="G9" s="11"/>
       <c r="H9" s="14"/>
@@ -1558,10 +1911,10 @@
     </row>
     <row r="11" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="4"/>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="43"/>
+      <c r="E11" s="47"/>
       <c r="F11" s="17"/>
       <c r="G11" s="18"/>
       <c r="H11" s="44" t="s">
@@ -1574,12 +1927,12 @@
     </row>
     <row r="12" spans="3:13" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="4"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="41"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="40"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="41"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="40"/>
       <c r="J12" s="15"/>
       <c r="K12" s="11"/>
       <c r="L12" s="14"/>
@@ -1599,10 +1952,10 @@
     </row>
     <row r="14" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="4"/>
-      <c r="D14" s="42" t="s">
+      <c r="D14" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="43"/>
+      <c r="E14" s="47"/>
       <c r="F14" s="16"/>
       <c r="G14" s="11"/>
       <c r="H14" s="14"/>
@@ -1614,8 +1967,8 @@
     </row>
     <row r="15" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="4"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="41"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="40"/>
       <c r="F15" s="16"/>
       <c r="G15" s="11"/>
       <c r="H15" s="14"/>
@@ -1639,10 +1992,10 @@
     </row>
     <row r="17" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="4"/>
-      <c r="D17" s="42" t="s">
+      <c r="D17" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="43"/>
+      <c r="E17" s="47"/>
       <c r="F17" s="17"/>
       <c r="G17" s="11"/>
       <c r="H17" s="14"/>
@@ -1654,8 +2007,8 @@
     </row>
     <row r="18" spans="1:13" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="4"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="41"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="40"/>
       <c r="F18" s="19"/>
       <c r="H18" s="14"/>
       <c r="I18" s="11"/>
@@ -1676,14 +2029,14 @@
     </row>
     <row r="20" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="4"/>
-      <c r="D20" s="42" t="s">
+      <c r="D20" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="43"/>
-      <c r="F20" s="46" t="s">
+      <c r="E20" s="47"/>
+      <c r="F20" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="47"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="44" t="s">
         <v>1</v>
       </c>
@@ -1695,12 +2048,12 @@
     </row>
     <row r="21" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="4"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="41"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="40"/>
       <c r="J21" s="16"/>
       <c r="K21" s="11"/>
       <c r="L21" s="14"/>
@@ -1718,10 +2071,10 @@
     </row>
     <row r="23" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="4"/>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="43"/>
+      <c r="E23" s="47"/>
       <c r="F23" s="8"/>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
@@ -1735,16 +2088,16 @@
     </row>
     <row r="24" spans="1:13" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="4"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="41"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="40"/>
       <c r="F24" s="5"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
       <c r="J24" s="6"/>
       <c r="K24" s="22"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="41"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="40"/>
     </row>
     <row r="25" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="12"/>
@@ -1771,8 +2124,8 @@
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="41"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="40"/>
       <c r="F27" s="11"/>
       <c r="J27" s="14"/>
       <c r="K27" s="11"/>
@@ -1795,10 +2148,10 @@
       </c>
       <c r="B29" s="45"/>
       <c r="C29" s="24"/>
-      <c r="D29" s="42" t="s">
+      <c r="D29" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="43"/>
+      <c r="E29" s="47"/>
       <c r="F29" s="8"/>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
@@ -1809,11 +2162,11 @@
       <c r="M29" s="11"/>
     </row>
     <row r="30" spans="1:13" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="40"/>
-      <c r="B30" s="41"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="40"/>
       <c r="C30" s="24"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="41"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="40"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
@@ -1831,44 +2184,44 @@
       <c r="M31" s="7"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="42" t="s">
+      <c r="A32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="43"/>
+      <c r="B32" s="47"/>
       <c r="C32" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="42" t="s">
+      <c r="D32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="43"/>
-      <c r="F32" s="46" t="s">
+      <c r="E32" s="47"/>
+      <c r="F32" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="47"/>
-      <c r="L32" s="42" t="s">
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="M32" s="43"/>
+      <c r="M32" s="47"/>
     </row>
     <row r="33" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="50"/>
-      <c r="B33" s="48"/>
+      <c r="A33" s="48"/>
+      <c r="B33" s="39"/>
       <c r="C33" s="16"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="47"/>
-      <c r="L33" s="40"/>
-      <c r="M33" s="48"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="39"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="20"/>
@@ -1888,38 +2241,25 @@
     </row>
     <row r="36" spans="1:13" ht="213.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="4"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="41"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="40"/>
       <c r="F36" s="11"/>
     </row>
     <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="48"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="39"/>
     </row>
     <row r="91" ht="0.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F32:K32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D8:E8"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H11:I11"/>
@@ -1936,12 +2276,25 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F32:K32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Assignment1_HT.xlsx
+++ b/Assignment1_HT.xlsx
@@ -563,30 +563,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2071,10 +2071,10 @@
     </row>
     <row r="2" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="4"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="41"/>
+      <c r="E2" s="47"/>
       <c r="F2" s="7"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -2086,7 +2086,7 @@
     <row r="3" spans="3:13" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="4"/>
       <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="5"/>
       <c r="G3" s="10"/>
       <c r="H3" s="6"/>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="5" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="4"/>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="41"/>
+      <c r="E5" s="47"/>
       <c r="F5" s="7"/>
       <c r="H5" s="14"/>
       <c r="I5" s="11"/>
@@ -2119,7 +2119,7 @@
     <row r="6" spans="3:13" ht="138.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="4"/>
       <c r="D6" s="38"/>
-      <c r="E6" s="39"/>
+      <c r="E6" s="40"/>
       <c r="F6" s="15"/>
       <c r="G6" s="11"/>
       <c r="H6" s="14"/>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="8" spans="3:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="4"/>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="41"/>
+      <c r="E8" s="47"/>
       <c r="F8" s="16"/>
       <c r="G8" s="11"/>
       <c r="H8" s="14"/>
@@ -2153,7 +2153,7 @@
     <row r="9" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="4"/>
       <c r="D9" s="38"/>
-      <c r="E9" s="39"/>
+      <c r="E9" s="40"/>
       <c r="F9" s="16"/>
       <c r="G9" s="11"/>
       <c r="H9" s="14"/>
@@ -2173,16 +2173,16 @@
     </row>
     <row r="11" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="4"/>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="41"/>
+      <c r="E11" s="47"/>
       <c r="F11" s="17"/>
       <c r="G11" s="18"/>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="43"/>
+      <c r="I11" s="45"/>
       <c r="J11" s="7"/>
       <c r="L11" s="14"/>
       <c r="M11" s="11"/>
@@ -2190,11 +2190,11 @@
     <row r="12" spans="3:13" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="4"/>
       <c r="D12" s="38"/>
-      <c r="E12" s="39"/>
+      <c r="E12" s="40"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="38"/>
-      <c r="I12" s="39"/>
+      <c r="I12" s="40"/>
       <c r="J12" s="15"/>
       <c r="K12" s="11"/>
       <c r="L12" s="14"/>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="14" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="4"/>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="41"/>
+      <c r="E14" s="47"/>
       <c r="F14" s="16"/>
       <c r="G14" s="11"/>
       <c r="H14" s="14"/>
@@ -2230,7 +2230,7 @@
     <row r="15" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="4"/>
       <c r="D15" s="38"/>
-      <c r="E15" s="39"/>
+      <c r="E15" s="40"/>
       <c r="F15" s="16"/>
       <c r="G15" s="11"/>
       <c r="H15" s="14"/>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="17" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="4"/>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="41"/>
+      <c r="E17" s="47"/>
       <c r="F17" s="17"/>
       <c r="G17" s="11"/>
       <c r="H17" s="14"/>
@@ -2270,7 +2270,7 @@
     <row r="18" spans="1:13" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="4"/>
       <c r="D18" s="38"/>
-      <c r="E18" s="39"/>
+      <c r="E18" s="40"/>
       <c r="F18" s="19"/>
       <c r="H18" s="14"/>
       <c r="I18" s="11"/>
@@ -2291,18 +2291,18 @@
     </row>
     <row r="20" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="4"/>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="44" t="s">
+      <c r="E20" s="47"/>
+      <c r="F20" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="45"/>
-      <c r="H20" s="42" t="s">
+      <c r="G20" s="43"/>
+      <c r="H20" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="I20" s="43"/>
+      <c r="I20" s="45"/>
       <c r="J20" s="16"/>
       <c r="K20" s="11"/>
       <c r="L20" s="14"/>
@@ -2311,11 +2311,11 @@
     <row r="21" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="4"/>
       <c r="D21" s="38"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="45"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
+      <c r="I21" s="40"/>
       <c r="J21" s="16"/>
       <c r="K21" s="11"/>
       <c r="L21" s="14"/>
@@ -2333,25 +2333,25 @@
     </row>
     <row r="23" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="4"/>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="41"/>
+      <c r="E23" s="47"/>
       <c r="F23" s="8"/>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
       <c r="I23" s="21"/>
       <c r="J23" s="9"/>
       <c r="K23" s="17"/>
-      <c r="L23" s="42" t="s">
+      <c r="L23" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="43"/>
+      <c r="M23" s="45"/>
     </row>
     <row r="24" spans="1:13" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="4"/>
       <c r="D24" s="38"/>
-      <c r="E24" s="39"/>
+      <c r="E24" s="40"/>
       <c r="F24" s="5"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -2359,7 +2359,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="22"/>
       <c r="L24" s="38"/>
-      <c r="M24" s="39"/>
+      <c r="M24" s="40"/>
     </row>
     <row r="25" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="12"/>
@@ -2372,10 +2372,10 @@
     <row r="26" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3"/>
       <c r="C26" s="23"/>
-      <c r="D26" s="42" t="s">
+      <c r="D26" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="43"/>
+      <c r="E26" s="45"/>
       <c r="F26" s="11"/>
       <c r="J26" s="14"/>
       <c r="K26" s="11"/>
@@ -2387,7 +2387,7 @@
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
       <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
+      <c r="E27" s="40"/>
       <c r="F27" s="11"/>
       <c r="J27" s="14"/>
       <c r="K27" s="11"/>
@@ -2405,15 +2405,15 @@
       <c r="M28" s="11"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="42" t="s">
+      <c r="A29" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="43"/>
+      <c r="B29" s="45"/>
       <c r="C29" s="24"/>
-      <c r="D29" s="40" t="s">
+      <c r="D29" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="41"/>
+      <c r="E29" s="47"/>
       <c r="F29" s="8"/>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="30" spans="1:13" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="38"/>
-      <c r="B30" s="39"/>
+      <c r="B30" s="40"/>
       <c r="C30" s="24"/>
       <c r="D30" s="38"/>
-      <c r="E30" s="39"/>
+      <c r="E30" s="40"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
@@ -2446,44 +2446,44 @@
       <c r="M31" s="7"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="40" t="s">
+      <c r="A32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="41"/>
+      <c r="B32" s="47"/>
       <c r="C32" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="40" t="s">
+      <c r="D32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="41"/>
-      <c r="F32" s="44" t="s">
+      <c r="E32" s="47"/>
+      <c r="F32" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="40" t="s">
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="M32" s="41"/>
+      <c r="M32" s="47"/>
     </row>
     <row r="33" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="48"/>
-      <c r="B33" s="46"/>
+      <c r="B33" s="39"/>
       <c r="C33" s="16"/>
       <c r="D33" s="38"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="45"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="43"/>
       <c r="L33" s="38"/>
-      <c r="M33" s="46"/>
+      <c r="M33" s="39"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="20"/>
@@ -2495,46 +2495,33 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C35" s="4"/>
-      <c r="D35" s="42" t="s">
+      <c r="D35" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="43"/>
+      <c r="E35" s="45"/>
       <c r="F35" s="11"/>
     </row>
     <row r="36" spans="1:13" ht="213.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="4"/>
       <c r="D36" s="38"/>
-      <c r="E36" s="39"/>
+      <c r="E36" s="40"/>
       <c r="F36" s="11"/>
     </row>
     <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
       <c r="H38" s="38"/>
-      <c r="I38" s="46"/>
+      <c r="I38" s="39"/>
     </row>
     <row r="91" ht="0.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F32:K32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D8:E8"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H11:I11"/>
@@ -2551,12 +2538,25 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F32:K32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Assignment1_HT.xlsx
+++ b/Assignment1_HT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentGeorgeTolkach\Desktop\CG_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentGeorgeTolkach\Desktop\CG_HT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D36BECA-A1BB-4C5D-8C56-BF3B0EDC59DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FA3D0F-BD22-48F8-94A8-2E5DED0BAD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -563,30 +563,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1369,6 +1369,270 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>312964</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>299357</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1033361</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>2340428</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5130ABA0-B724-0412-1B95-547F7DC25E16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2149928" y="35392178"/>
+          <a:ext cx="3224112" cy="2041071"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1999875</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>5116287</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E764E63-5D56-CC15-6A5C-1ED7B502B269}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1836965" y="39515144"/>
+          <a:ext cx="1999874" cy="5116286"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1836965</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>27213</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3516522</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{349F8443-87B8-DC23-345E-570DA5FD91E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3673929" y="39542356"/>
+          <a:ext cx="1932214" cy="3489309"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>136071</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1437839</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DCAFC98-5577-B3A6-666A-90FFBB68801A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12355286" y="27826608"/>
+          <a:ext cx="2435678" cy="1410624"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>2262273</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{792AFDB5-7661-0F7F-C75F-3BEE3FCA40CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11783787" y="39515143"/>
+          <a:ext cx="2262272" cy="5197928"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1986645</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1375404</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>4136572</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00BBA1CF-97A8-AB8D-F7EE-8D2FF4C02F41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13770431" y="39515143"/>
+          <a:ext cx="2259866" cy="4136572"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2062,7 +2326,7 @@
     <col min="10" max="10" width="9.140625" customWidth="1"/>
     <col min="11" max="11" width="3.7109375" customWidth="1"/>
     <col min="12" max="12" width="43.140625" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2071,10 +2335,10 @@
     </row>
     <row r="2" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="4"/>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="47"/>
+      <c r="E2" s="41"/>
       <c r="F2" s="7"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -2086,7 +2350,7 @@
     <row r="3" spans="3:13" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="4"/>
       <c r="D3" s="38"/>
-      <c r="E3" s="40"/>
+      <c r="E3" s="39"/>
       <c r="F3" s="5"/>
       <c r="G3" s="10"/>
       <c r="H3" s="6"/>
@@ -2106,10 +2370,10 @@
     </row>
     <row r="5" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="4"/>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="47"/>
+      <c r="E5" s="41"/>
       <c r="F5" s="7"/>
       <c r="H5" s="14"/>
       <c r="I5" s="11"/>
@@ -2119,7 +2383,7 @@
     <row r="6" spans="3:13" ht="138.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="4"/>
       <c r="D6" s="38"/>
-      <c r="E6" s="40"/>
+      <c r="E6" s="39"/>
       <c r="F6" s="15"/>
       <c r="G6" s="11"/>
       <c r="H6" s="14"/>
@@ -2139,10 +2403,10 @@
     </row>
     <row r="8" spans="3:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="4"/>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="47"/>
+      <c r="E8" s="41"/>
       <c r="F8" s="16"/>
       <c r="G8" s="11"/>
       <c r="H8" s="14"/>
@@ -2153,7 +2417,7 @@
     <row r="9" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="4"/>
       <c r="D9" s="38"/>
-      <c r="E9" s="40"/>
+      <c r="E9" s="39"/>
       <c r="F9" s="16"/>
       <c r="G9" s="11"/>
       <c r="H9" s="14"/>
@@ -2173,16 +2437,16 @@
     </row>
     <row r="11" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="4"/>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="47"/>
+      <c r="E11" s="41"/>
       <c r="F11" s="17"/>
       <c r="G11" s="18"/>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="45"/>
+      <c r="I11" s="43"/>
       <c r="J11" s="7"/>
       <c r="L11" s="14"/>
       <c r="M11" s="11"/>
@@ -2190,11 +2454,11 @@
     <row r="12" spans="3:13" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="4"/>
       <c r="D12" s="38"/>
-      <c r="E12" s="40"/>
+      <c r="E12" s="39"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="38"/>
-      <c r="I12" s="40"/>
+      <c r="I12" s="39"/>
       <c r="J12" s="15"/>
       <c r="K12" s="11"/>
       <c r="L12" s="14"/>
@@ -2214,10 +2478,10 @@
     </row>
     <row r="14" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="4"/>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="47"/>
+      <c r="E14" s="41"/>
       <c r="F14" s="16"/>
       <c r="G14" s="11"/>
       <c r="H14" s="14"/>
@@ -2230,7 +2494,7 @@
     <row r="15" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="4"/>
       <c r="D15" s="38"/>
-      <c r="E15" s="40"/>
+      <c r="E15" s="39"/>
       <c r="F15" s="16"/>
       <c r="G15" s="11"/>
       <c r="H15" s="14"/>
@@ -2254,10 +2518,10 @@
     </row>
     <row r="17" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="4"/>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="47"/>
+      <c r="E17" s="41"/>
       <c r="F17" s="17"/>
       <c r="G17" s="11"/>
       <c r="H17" s="14"/>
@@ -2270,7 +2534,7 @@
     <row r="18" spans="1:13" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="4"/>
       <c r="D18" s="38"/>
-      <c r="E18" s="40"/>
+      <c r="E18" s="39"/>
       <c r="F18" s="19"/>
       <c r="H18" s="14"/>
       <c r="I18" s="11"/>
@@ -2291,18 +2555,18 @@
     </row>
     <row r="20" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="4"/>
-      <c r="D20" s="46" t="s">
+      <c r="D20" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="41" t="s">
+      <c r="E20" s="41"/>
+      <c r="F20" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44" t="s">
+      <c r="G20" s="45"/>
+      <c r="H20" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="I20" s="45"/>
+      <c r="I20" s="43"/>
       <c r="J20" s="16"/>
       <c r="K20" s="11"/>
       <c r="L20" s="14"/>
@@ -2311,11 +2575,11 @@
     <row r="21" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="4"/>
       <c r="D21" s="38"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="43"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="45"/>
       <c r="H21" s="38"/>
-      <c r="I21" s="40"/>
+      <c r="I21" s="39"/>
       <c r="J21" s="16"/>
       <c r="K21" s="11"/>
       <c r="L21" s="14"/>
@@ -2333,25 +2597,25 @@
     </row>
     <row r="23" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="4"/>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="47"/>
+      <c r="E23" s="41"/>
       <c r="F23" s="8"/>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
       <c r="I23" s="21"/>
       <c r="J23" s="9"/>
       <c r="K23" s="17"/>
-      <c r="L23" s="44" t="s">
+      <c r="L23" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="45"/>
+      <c r="M23" s="43"/>
     </row>
     <row r="24" spans="1:13" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="4"/>
       <c r="D24" s="38"/>
-      <c r="E24" s="40"/>
+      <c r="E24" s="39"/>
       <c r="F24" s="5"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -2359,7 +2623,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="22"/>
       <c r="L24" s="38"/>
-      <c r="M24" s="40"/>
+      <c r="M24" s="39"/>
     </row>
     <row r="25" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="12"/>
@@ -2372,10 +2636,10 @@
     <row r="26" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3"/>
       <c r="C26" s="23"/>
-      <c r="D26" s="44" t="s">
+      <c r="D26" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="45"/>
+      <c r="E26" s="43"/>
       <c r="F26" s="11"/>
       <c r="J26" s="14"/>
       <c r="K26" s="11"/>
@@ -2387,7 +2651,7 @@
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
       <c r="D27" s="38"/>
-      <c r="E27" s="40"/>
+      <c r="E27" s="39"/>
       <c r="F27" s="11"/>
       <c r="J27" s="14"/>
       <c r="K27" s="11"/>
@@ -2405,15 +2669,15 @@
       <c r="M28" s="11"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="45"/>
+      <c r="B29" s="43"/>
       <c r="C29" s="24"/>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="47"/>
+      <c r="E29" s="41"/>
       <c r="F29" s="8"/>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
@@ -2425,10 +2689,10 @@
     </row>
     <row r="30" spans="1:13" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="38"/>
-      <c r="B30" s="40"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="24"/>
       <c r="D30" s="38"/>
-      <c r="E30" s="40"/>
+      <c r="E30" s="39"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
@@ -2446,44 +2710,44 @@
       <c r="M31" s="7"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="47"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="46" t="s">
+      <c r="D32" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="47"/>
-      <c r="F32" s="41" t="s">
+      <c r="E32" s="41"/>
+      <c r="F32" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="46" t="s">
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="M32" s="47"/>
+      <c r="M32" s="41"/>
     </row>
     <row r="33" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="48"/>
-      <c r="B33" s="39"/>
+      <c r="B33" s="46"/>
       <c r="C33" s="16"/>
       <c r="D33" s="38"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="43"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="45"/>
       <c r="L33" s="38"/>
-      <c r="M33" s="39"/>
+      <c r="M33" s="46"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="20"/>
@@ -2495,33 +2759,46 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C35" s="4"/>
-      <c r="D35" s="44" t="s">
+      <c r="D35" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="45"/>
+      <c r="E35" s="43"/>
       <c r="F35" s="11"/>
     </row>
     <row r="36" spans="1:13" ht="213.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="4"/>
       <c r="D36" s="38"/>
-      <c r="E36" s="40"/>
+      <c r="E36" s="39"/>
       <c r="F36" s="11"/>
     </row>
     <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
       <c r="H38" s="38"/>
-      <c r="I38" s="39"/>
+      <c r="I38" s="46"/>
     </row>
     <row r="91" ht="0.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F32:K32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H11:I11"/>
@@ -2538,25 +2815,12 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F32:K32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Assignment1_HT.xlsx
+++ b/Assignment1_HT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentGeorgeTolkach\Desktop\CG_HT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentGeorgeTolkach\Desktop\CG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FA3D0F-BD22-48F8-94A8-2E5DED0BAD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDFB132-7E80-446E-8CF3-1CA23F0D5B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assignment generation" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>z = -1</t>
   </si>
@@ -187,6 +187,21 @@
   <si>
     <t>.normalsed</t>
   </si>
+  <si>
+    <t>Final Coords</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>Final coords</t>
+  </si>
 </sst>
 </file>
 
@@ -226,7 +241,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -246,6 +261,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -444,7 +465,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -563,6 +584,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -571,24 +610,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -597,6 +618,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -616,6 +640,1045 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$L$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet2!$K$6:$K$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>-0.60963916225082004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.33859142412797161</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.68636820925553321</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.60973236009732357</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.29082166004599624</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.47503314184710566</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.35537017726798747</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.54241022251597271</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.36280857952246054</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.30923773882213901</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.67674775367083051</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.60983397190293742</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.37681436210847979</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.32582386892571213</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.60990712074303399</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.383243544491919</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.58146385678676638</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.33811351242173299</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.65024853140533223</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.58223684210526316</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.2942862602713549</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.46201768488745981</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.35328884652049569</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.52355181399077977</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.3603486646884273</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.31119956576804775</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.64559234144395683</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.5854700854700855</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-0.37319732676749912</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.32623260608142929</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-0.58621340887629836</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.37922166980970345</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$L$6:$L$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="32"/>
+                <c:pt idx="0">
+                  <c:v>-0.21170830179157205</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.15907576094201289</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.16825955734406439</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.15523114355231143</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.1014007944804516</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-8.3075563411400793E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-6.5693430656934296E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-4.5604758757435554E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-2.3269931201942529E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.6545203860547565E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.9147490685952224E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.4695615155385273E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.4621848739495799E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.9020666542543287E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.5128998968008259E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9.0469998142299834E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.25764785859959211</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.20480710967481319</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.21848169905106191</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.20548245614035085</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.14962736480030575</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.13565112540192928</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.11687321258341277</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.1012226899178192</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-7.6594955489614244E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-6.9115252397322233E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-3.3107299561228556E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-2.6223776223776227E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-2.1104467112205414E-3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.0922521903453013E-3</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.2275731822474031E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.2230413166466652E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5E70-443D-AC75-A4AD91D83C5A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="217011280"/>
+        <c:axId val="203500304"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="217011280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="203500304"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="203500304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="217011280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1415,94 +2478,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1999875</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>5116287</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E764E63-5D56-CC15-6A5C-1ED7B502B269}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1836965" y="39515144"/>
-          <a:ext cx="1999874" cy="5116286"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1836965</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>27213</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>3516522</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{349F8443-87B8-DC23-345E-570DA5FD91E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3673929" y="39542356"/>
-          <a:ext cx="1932214" cy="3489309"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
       <xdr:row>23</xdr:row>
@@ -1528,7 +2503,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1547,23 +2522,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>69273</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>173181</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1899587</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>5143500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF83DDBC-84B5-4DED-7929-EDEC19C02D03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1887682" y="39520090"/>
+          <a:ext cx="1830314" cy="4970319"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1887682</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>138544</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>36545</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>51954</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FD2E764-1BAE-1B97-C633-4106C41351B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3706091" y="39485453"/>
+          <a:ext cx="1924227" cy="5108865"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>74367</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>31580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>2262273</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>2169867</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>70976</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
+        <xdr:cNvPr id="10" name="Picture 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{792AFDB5-7661-0F7F-C75F-3BEE3FCA40CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE225715-6D91-79F7-0A88-E71B00CD0634}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1579,8 +2642,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11783787" y="39515143"/>
-          <a:ext cx="2262272" cy="5197928"/>
+          <a:off x="11829338" y="39386639"/>
+          <a:ext cx="2095500" cy="5395808"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1592,22 +2655,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>1986645</xdr:colOff>
+      <xdr:colOff>2263589</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>56028</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>1375404</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>4136572</xdr:rowOff>
+      <xdr:colOff>1398422</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
+        <xdr:cNvPr id="11" name="Picture 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00BBA1CF-97A8-AB8D-F7EE-8D2FF4C02F41}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B51BFBC-094D-1F26-7801-FBBBC0B738ED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1623,14 +2686,55 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13770431" y="39515143"/>
-          <a:ext cx="2259866" cy="4136572"/>
+          <a:off x="14018560" y="39411087"/>
+          <a:ext cx="2014744" cy="5322795"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE2796CE-C0B0-0D0A-202A-ED8B86B8919F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2335,10 +3439,10 @@
     </row>
     <row r="2" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="4"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="41"/>
+      <c r="E2" s="47"/>
       <c r="F2" s="7"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -2350,7 +3454,7 @@
     <row r="3" spans="3:13" ht="408.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="4"/>
       <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="5"/>
       <c r="G3" s="10"/>
       <c r="H3" s="6"/>
@@ -2370,10 +3474,10 @@
     </row>
     <row r="5" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="4"/>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="41"/>
+      <c r="E5" s="47"/>
       <c r="F5" s="7"/>
       <c r="H5" s="14"/>
       <c r="I5" s="11"/>
@@ -2383,7 +3487,7 @@
     <row r="6" spans="3:13" ht="138.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="4"/>
       <c r="D6" s="38"/>
-      <c r="E6" s="39"/>
+      <c r="E6" s="40"/>
       <c r="F6" s="15"/>
       <c r="G6" s="11"/>
       <c r="H6" s="14"/>
@@ -2403,10 +3507,10 @@
     </row>
     <row r="8" spans="3:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="4"/>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="41"/>
+      <c r="E8" s="47"/>
       <c r="F8" s="16"/>
       <c r="G8" s="11"/>
       <c r="H8" s="14"/>
@@ -2417,7 +3521,7 @@
     <row r="9" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="4"/>
       <c r="D9" s="38"/>
-      <c r="E9" s="39"/>
+      <c r="E9" s="40"/>
       <c r="F9" s="16"/>
       <c r="G9" s="11"/>
       <c r="H9" s="14"/>
@@ -2437,16 +3541,16 @@
     </row>
     <row r="11" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="4"/>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="41"/>
+      <c r="E11" s="47"/>
       <c r="F11" s="17"/>
       <c r="G11" s="18"/>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="43"/>
+      <c r="I11" s="45"/>
       <c r="J11" s="7"/>
       <c r="L11" s="14"/>
       <c r="M11" s="11"/>
@@ -2454,11 +3558,11 @@
     <row r="12" spans="3:13" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="4"/>
       <c r="D12" s="38"/>
-      <c r="E12" s="39"/>
+      <c r="E12" s="40"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="38"/>
-      <c r="I12" s="39"/>
+      <c r="I12" s="40"/>
       <c r="J12" s="15"/>
       <c r="K12" s="11"/>
       <c r="L12" s="14"/>
@@ -2478,10 +3582,10 @@
     </row>
     <row r="14" spans="3:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="4"/>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="41"/>
+      <c r="E14" s="47"/>
       <c r="F14" s="16"/>
       <c r="G14" s="11"/>
       <c r="H14" s="14"/>
@@ -2494,7 +3598,7 @@
     <row r="15" spans="3:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="4"/>
       <c r="D15" s="38"/>
-      <c r="E15" s="39"/>
+      <c r="E15" s="40"/>
       <c r="F15" s="16"/>
       <c r="G15" s="11"/>
       <c r="H15" s="14"/>
@@ -2518,10 +3622,10 @@
     </row>
     <row r="17" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="4"/>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="41"/>
+      <c r="E17" s="47"/>
       <c r="F17" s="17"/>
       <c r="G17" s="11"/>
       <c r="H17" s="14"/>
@@ -2534,7 +3638,7 @@
     <row r="18" spans="1:13" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="4"/>
       <c r="D18" s="38"/>
-      <c r="E18" s="39"/>
+      <c r="E18" s="40"/>
       <c r="F18" s="19"/>
       <c r="H18" s="14"/>
       <c r="I18" s="11"/>
@@ -2555,18 +3659,18 @@
     </row>
     <row r="20" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="4"/>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="44" t="s">
+      <c r="E20" s="47"/>
+      <c r="F20" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="45"/>
-      <c r="H20" s="42" t="s">
+      <c r="G20" s="43"/>
+      <c r="H20" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="I20" s="43"/>
+      <c r="I20" s="45"/>
       <c r="J20" s="16"/>
       <c r="K20" s="11"/>
       <c r="L20" s="14"/>
@@ -2575,11 +3679,11 @@
     <row r="21" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="4"/>
       <c r="D21" s="38"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="45"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
+      <c r="I21" s="40"/>
       <c r="J21" s="16"/>
       <c r="K21" s="11"/>
       <c r="L21" s="14"/>
@@ -2597,25 +3701,25 @@
     </row>
     <row r="23" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="4"/>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="41"/>
+      <c r="E23" s="47"/>
       <c r="F23" s="8"/>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
       <c r="I23" s="21"/>
       <c r="J23" s="9"/>
       <c r="K23" s="17"/>
-      <c r="L23" s="42" t="s">
+      <c r="L23" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="43"/>
+      <c r="M23" s="45"/>
     </row>
     <row r="24" spans="1:13" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="4"/>
       <c r="D24" s="38"/>
-      <c r="E24" s="39"/>
+      <c r="E24" s="40"/>
       <c r="F24" s="5"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -2623,7 +3727,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="22"/>
       <c r="L24" s="38"/>
-      <c r="M24" s="39"/>
+      <c r="M24" s="40"/>
     </row>
     <row r="25" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="12"/>
@@ -2636,10 +3740,10 @@
     <row r="26" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3"/>
       <c r="C26" s="23"/>
-      <c r="D26" s="42" t="s">
+      <c r="D26" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="43"/>
+      <c r="E26" s="45"/>
       <c r="F26" s="11"/>
       <c r="J26" s="14"/>
       <c r="K26" s="11"/>
@@ -2651,7 +3755,7 @@
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
       <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
+      <c r="E27" s="40"/>
       <c r="F27" s="11"/>
       <c r="J27" s="14"/>
       <c r="K27" s="11"/>
@@ -2669,15 +3773,15 @@
       <c r="M28" s="11"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="42" t="s">
+      <c r="A29" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="43"/>
+      <c r="B29" s="45"/>
       <c r="C29" s="24"/>
-      <c r="D29" s="40" t="s">
+      <c r="D29" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="41"/>
+      <c r="E29" s="47"/>
       <c r="F29" s="8"/>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
@@ -2689,10 +3793,10 @@
     </row>
     <row r="30" spans="1:13" ht="322.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="38"/>
-      <c r="B30" s="39"/>
+      <c r="B30" s="40"/>
       <c r="C30" s="24"/>
       <c r="D30" s="38"/>
-      <c r="E30" s="39"/>
+      <c r="E30" s="40"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
@@ -2710,44 +3814,44 @@
       <c r="M31" s="7"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="40" t="s">
+      <c r="A32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="41"/>
+      <c r="B32" s="47"/>
       <c r="C32" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="40" t="s">
+      <c r="D32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="41"/>
-      <c r="F32" s="44" t="s">
+      <c r="E32" s="47"/>
+      <c r="F32" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="40" t="s">
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="M32" s="41"/>
+      <c r="M32" s="47"/>
     </row>
     <row r="33" spans="1:13" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="48"/>
-      <c r="B33" s="46"/>
+      <c r="B33" s="39"/>
       <c r="C33" s="16"/>
       <c r="D33" s="38"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="45"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="43"/>
       <c r="L33" s="38"/>
-      <c r="M33" s="46"/>
+      <c r="M33" s="39"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="20"/>
@@ -2759,46 +3863,33 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C35" s="4"/>
-      <c r="D35" s="42" t="s">
+      <c r="D35" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="43"/>
+      <c r="E35" s="45"/>
       <c r="F35" s="11"/>
     </row>
     <row r="36" spans="1:13" ht="213.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="4"/>
       <c r="D36" s="38"/>
-      <c r="E36" s="39"/>
+      <c r="E36" s="40"/>
       <c r="F36" s="11"/>
     </row>
     <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
       <c r="H38" s="38"/>
-      <c r="I38" s="46"/>
+      <c r="I38" s="39"/>
     </row>
     <row r="91" ht="0.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F32:K32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D8:E8"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H11:I11"/>
@@ -2815,12 +3906,25 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F32:K32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2831,13 +3935,747 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43DB12A5-2734-4A80-B355-23ECE7ADE458}">
-  <dimension ref="A1"/>
+  <dimension ref="E4:M37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="4" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>24.16</v>
+      </c>
+      <c r="F6">
+        <v>8.39</v>
+      </c>
+      <c r="G6">
+        <v>-39.630000000000003</v>
+      </c>
+      <c r="K6">
+        <f>E6 / G6</f>
+        <v>-0.60963916225082004</v>
+      </c>
+      <c r="L6">
+        <f>F6 / G6</f>
+        <v>-0.21170830179157205</v>
+      </c>
+      <c r="M6" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <v>15.24</v>
+      </c>
+      <c r="F7">
+        <v>7.16</v>
+      </c>
+      <c r="G7">
+        <v>-45.01</v>
+      </c>
+      <c r="K7">
+        <f t="shared" ref="K7:K37" si="0">E7 / G7</f>
+        <v>-0.33859142412797161</v>
+      </c>
+      <c r="L7">
+        <f t="shared" ref="L7:L37" si="1">F7 / G7</f>
+        <v>-0.15907576094201289</v>
+      </c>
+      <c r="M7" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>27.29</v>
+      </c>
+      <c r="F8">
+        <v>6.69</v>
+      </c>
+      <c r="G8">
+        <v>-39.76</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>-0.68636820925553321</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="1"/>
+        <v>-0.16825955734406439</v>
+      </c>
+      <c r="M8" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E9">
+        <v>25.06</v>
+      </c>
+      <c r="F9">
+        <v>6.38</v>
+      </c>
+      <c r="G9">
+        <v>-41.1</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>-0.60973236009732357</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="1"/>
+        <v>-0.15523114355231143</v>
+      </c>
+      <c r="M9" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E10">
+        <v>13.91</v>
+      </c>
+      <c r="F10">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="G10">
+        <v>-47.83</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>-0.29082166004599624</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="1"/>
+        <v>-0.1014007944804516</v>
+      </c>
+      <c r="M10" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <v>21.5</v>
+      </c>
+      <c r="F11">
+        <v>3.76</v>
+      </c>
+      <c r="G11">
+        <v>-45.26</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>-0.47503314184710566</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="1"/>
+        <v>-8.3075563411400793E-2</v>
+      </c>
+      <c r="M11" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <v>17.04</v>
+      </c>
+      <c r="F12">
+        <v>3.15</v>
+      </c>
+      <c r="G12">
+        <v>-47.95</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>-0.35537017726798747</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="1"/>
+        <v>-6.5693430656934296E-2</v>
+      </c>
+      <c r="M12" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E13">
+        <v>24.62</v>
+      </c>
+      <c r="F13">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="G13">
+        <v>-45.39</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>-0.54241022251597271</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="1"/>
+        <v>-4.5604758757435554E-2</v>
+      </c>
+      <c r="M13" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E14">
+        <v>17.93</v>
+      </c>
+      <c r="F14">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G14">
+        <v>-49.42</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>-0.36280857952246054</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="1"/>
+        <v>-2.3269931201942529E-2</v>
+      </c>
+      <c r="M14" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E15">
+        <v>15.7</v>
+      </c>
+      <c r="F15">
+        <v>0.84</v>
+      </c>
+      <c r="G15">
+        <v>-50.77</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>-0.30923773882213901</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>-1.6545203860547565E-2</v>
+      </c>
+      <c r="M15" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <v>30.88</v>
+      </c>
+      <c r="F16">
+        <v>-1.33</v>
+      </c>
+      <c r="G16">
+        <v>-45.63</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>-0.67674775367083051</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>2.9147490685952224E-2</v>
+      </c>
+      <c r="M16" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <v>28.65</v>
+      </c>
+      <c r="F17">
+        <v>-1.63</v>
+      </c>
+      <c r="G17">
+        <v>-46.98</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>-0.60983397190293742</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>3.4695615155385273E-2</v>
+      </c>
+      <c r="M17" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <v>19.73</v>
+      </c>
+      <c r="F18">
+        <v>-2.86</v>
+      </c>
+      <c r="G18">
+        <v>-52.36</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>-0.37681436210847979</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="1"/>
+        <v>5.4621848739495799E-2</v>
+      </c>
+      <c r="M18" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>17.5</v>
+      </c>
+      <c r="F19">
+        <v>-3.17</v>
+      </c>
+      <c r="G19">
+        <v>-53.71</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>-0.32582386892571213</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="1"/>
+        <v>5.9020666542543287E-2</v>
+      </c>
+      <c r="M19" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>29.55</v>
+      </c>
+      <c r="F20">
+        <v>-3.64</v>
+      </c>
+      <c r="G20">
+        <v>-48.45</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>-0.60990712074303399</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="1"/>
+        <v>7.5128998968008259E-2</v>
+      </c>
+      <c r="M20" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <v>20.63</v>
+      </c>
+      <c r="F21">
+        <v>-4.87</v>
+      </c>
+      <c r="G21">
+        <v>-53.83</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>-0.383243544491919</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="1"/>
+        <v>9.0469998142299834E-2</v>
+      </c>
+      <c r="M21" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E22">
+        <v>25.66</v>
+      </c>
+      <c r="F22">
+        <v>11.37</v>
+      </c>
+      <c r="G22">
+        <v>-44.13</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>-0.58146385678676638</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="1"/>
+        <v>-0.25764785859959211</v>
+      </c>
+      <c r="M22" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <v>16.739999999999998</v>
+      </c>
+      <c r="F23">
+        <v>10.14</v>
+      </c>
+      <c r="G23">
+        <v>-49.51</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>-0.33811351242173299</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="1"/>
+        <v>-0.20480710967481319</v>
+      </c>
+      <c r="M23" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <v>28.78</v>
+      </c>
+      <c r="F24">
+        <v>9.67</v>
+      </c>
+      <c r="G24">
+        <v>-44.26</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="0"/>
+        <v>-0.65024853140533223</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="1"/>
+        <v>-0.21848169905106191</v>
+      </c>
+      <c r="M24" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <v>26.55</v>
+      </c>
+      <c r="F25">
+        <v>9.3699999999999992</v>
+      </c>
+      <c r="G25">
+        <v>-45.6</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="0"/>
+        <v>-0.58223684210526316</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="1"/>
+        <v>-0.20548245614035085</v>
+      </c>
+      <c r="M25" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E26">
+        <v>15.4</v>
+      </c>
+      <c r="F26">
+        <v>7.83</v>
+      </c>
+      <c r="G26">
+        <v>-52.33</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="0"/>
+        <v>-0.2942862602713549</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>-0.14962736480030575</v>
+      </c>
+      <c r="M26" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <v>22.99</v>
+      </c>
+      <c r="F27">
+        <v>6.75</v>
+      </c>
+      <c r="G27">
+        <v>-49.76</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="0"/>
+        <v>-0.46201768488745981</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="1"/>
+        <v>-0.13565112540192928</v>
+      </c>
+      <c r="M27" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E28">
+        <v>18.53</v>
+      </c>
+      <c r="F28">
+        <v>6.13</v>
+      </c>
+      <c r="G28">
+        <v>-52.45</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="0"/>
+        <v>-0.35328884652049569</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="1"/>
+        <v>-0.11687321258341277</v>
+      </c>
+      <c r="M28" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E29">
+        <v>26.12</v>
+      </c>
+      <c r="F29">
+        <v>5.05</v>
+      </c>
+      <c r="G29">
+        <v>-49.89</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="0"/>
+        <v>-0.52355181399077977</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="1"/>
+        <v>-0.1012226899178192</v>
+      </c>
+      <c r="M29" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <v>19.43</v>
+      </c>
+      <c r="F30">
+        <v>4.13</v>
+      </c>
+      <c r="G30">
+        <v>-53.92</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="0"/>
+        <v>-0.3603486646884273</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="1"/>
+        <v>-7.6594955489614244E-2</v>
+      </c>
+      <c r="M30" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E31">
+        <v>17.2</v>
+      </c>
+      <c r="F31">
+        <v>3.82</v>
+      </c>
+      <c r="G31">
+        <v>-55.27</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="0"/>
+        <v>-0.31119956576804775</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="1"/>
+        <v>-6.9115252397322233E-2</v>
+      </c>
+      <c r="M31" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E32">
+        <v>32.369999999999997</v>
+      </c>
+      <c r="F32">
+        <v>1.66</v>
+      </c>
+      <c r="G32">
+        <v>-50.14</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="0"/>
+        <v>-0.64559234144395683</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="1"/>
+        <v>-3.3107299561228556E-2</v>
+      </c>
+      <c r="M32" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E33">
+        <v>30.14</v>
+      </c>
+      <c r="F33">
+        <v>1.35</v>
+      </c>
+      <c r="G33">
+        <v>-51.48</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="0"/>
+        <v>-0.5854700854700855</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="1"/>
+        <v>-2.6223776223776227E-2</v>
+      </c>
+      <c r="M33" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E34">
+        <v>21.22</v>
+      </c>
+      <c r="F34">
+        <v>0.12</v>
+      </c>
+      <c r="G34">
+        <v>-56.86</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="0"/>
+        <v>-0.37319732676749912</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="1"/>
+        <v>-2.1104467112205414E-3</v>
+      </c>
+      <c r="M34" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E35">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="F35">
+        <v>-0.18</v>
+      </c>
+      <c r="G35">
+        <v>-58.21</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="0"/>
+        <v>-0.32623260608142929</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="1"/>
+        <v>3.0922521903453013E-3</v>
+      </c>
+      <c r="M35" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E36">
+        <v>31.04</v>
+      </c>
+      <c r="F36">
+        <v>-0.65</v>
+      </c>
+      <c r="G36">
+        <v>-52.95</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="0"/>
+        <v>-0.58621340887629836</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="1"/>
+        <v>1.2275731822474031E-2</v>
+      </c>
+      <c r="M36" s="51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="E37">
+        <v>22.12</v>
+      </c>
+      <c r="F37">
+        <v>-1.88</v>
+      </c>
+      <c r="G37">
+        <v>-58.33</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="0"/>
+        <v>-0.37922166980970345</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="1"/>
+        <v>3.2230413166466652E-2</v>
+      </c>
+      <c r="M37" s="51">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
